--- a/public/excels/default-members.xlsx
+++ b/public/excels/default-members.xlsx
@@ -5,7 +5,7 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\codes\private\party-lottery\src\assets\excels\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\codes\private\party-lottery\public\excels\"/>
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
@@ -75,7 +75,7 @@
     <t>皇室</t>
   </si>
   <si>
-    <t>https://i1.hdslb.com/bfs/archive/3d9709cb7d30d65583bf443a3e712f98e6976c8c.jpg</t>
+    <t>./images/zhu-houcong.png</t>
   </si>
   <si>
     <t>000002</t>
@@ -93,7 +93,7 @@
     <t>朱翊钧</t>
   </si>
   <si>
-    <t>https://pics4.baidu.com/feed/d0c8a786c9177f3e3e81c42cb86eb5d79e3d568f.jpeg@f_auto?token=a26146de77392b2cf57e9ae363d0dab0</t>
+    <t>./images/zhu-yijun.png</t>
   </si>
   <si>
     <t>000004</t>
@@ -312,7 +312,7 @@
     <t>东缉事厂 裕王府</t>
   </si>
   <si>
-    <t>https://q2.itc.cn/images01/20240318/00b7e1c04ec74a1bbc5c9672805c10bc.png</t>
+    <t>./images/feng-bao.png</t>
   </si>
   <si>
     <t>000024</t>
@@ -595,7 +595,7 @@
     <font>
       <u/>
       <sz val="11"/>
-      <color rgb="FF0000FF"/>
+      <color rgb="FF800080"/>
       <name val="宋体"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -603,7 +603,7 @@
     <font>
       <u/>
       <sz val="11"/>
-      <color rgb="FF800080"/>
+      <color rgb="FF0000FF"/>
       <name val="宋体"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -1063,10 +1063,10 @@
     <xf numFmtId="42" fontId="0" fillId="0" borderId="0">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="1">
@@ -1203,10 +1203,10 @@
     <xf numFmtId="0" fontId="2" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="6">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="6" applyFont="1">
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="6" applyFont="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="6">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1" quotePrefix="1">
@@ -1675,7 +1675,7 @@
       <c r="C8" t="s">
         <v>26</v>
       </c>
-      <c r="D8" s="3" t="s">
+      <c r="D8" s="4" t="s">
         <v>33</v>
       </c>
     </row>
@@ -1689,7 +1689,7 @@
       <c r="C9" t="s">
         <v>36</v>
       </c>
-      <c r="D9" s="3" t="s">
+      <c r="D9" s="4" t="s">
         <v>37</v>
       </c>
     </row>
@@ -1703,7 +1703,7 @@
       <c r="C10" t="s">
         <v>22</v>
       </c>
-      <c r="D10" s="4" t="s">
+      <c r="D10" s="3" t="s">
         <v>40</v>
       </c>
     </row>
@@ -1742,7 +1742,7 @@
       <c r="C13" t="s">
         <v>49</v>
       </c>
-      <c r="D13" s="3" t="s">
+      <c r="D13" s="4" t="s">
         <v>50</v>
       </c>
     </row>
@@ -2049,7 +2049,7 @@
       <c r="C36" t="s">
         <v>87</v>
       </c>
-      <c r="D36" s="3" t="s">
+      <c r="D36" s="4" t="s">
         <v>131</v>
       </c>
     </row>
@@ -2099,7 +2099,7 @@
       <c r="C40" t="s">
         <v>144</v>
       </c>
-      <c r="D40" s="3" t="s">
+      <c r="D40" s="4" t="s">
         <v>145</v>
       </c>
     </row>
@@ -2229,7 +2229,7 @@
     <hyperlink ref="D36" r:id="rId4" display="https://i1.hdslb.com/bfs/archive/48a28178cf3787ff65505f8271489e858e40bb61.jpg"/>
     <hyperlink ref="D16" r:id="rId5" display="https://i0.hdslb.com/bfs/archive/df3863c962c3374e7a21544940831a4412634925.jpg@1200w_630h"/>
     <hyperlink ref="D13" r:id="rId6" display="https://pic4.zhimg.com/v2-5826144298f140ca238949087e9c14a3_r.jpg"/>
-    <hyperlink ref="D2" r:id="rId7" display="https://i1.hdslb.com/bfs/archive/3d9709cb7d30d65583bf443a3e712f98e6976c8c.jpg"/>
+    <hyperlink ref="D2" r:id="rId7" display="./images/zhu-houcong.png"/>
     <hyperlink ref="D40" r:id="rId8" display="https://bj.bcebos.com/bjh-pixel/17095232360135075178_1_ainote_new.jpg"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/public/excels/default-members.xlsx
+++ b/public/excels/default-members.xlsx
@@ -34,7 +34,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="189" uniqueCount="175">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="189" uniqueCount="176">
   <si>
     <t>employeeId</t>
   </si>
@@ -195,7 +195,7 @@
     <t>谭伦</t>
   </si>
   <si>
-    <t>裕王府 浙直总督署 浙江按察使司</t>
+    <t>裕王府 浙直总督署 浙江按察使司 南直隶巡抚署</t>
   </si>
   <si>
     <t>https://picx.zhimg.com/v2-e4d53f7e314afdae5ca3730c853ff29f_1440w.jpg</t>
@@ -243,7 +243,7 @@
     <t>郑必昌</t>
   </si>
   <si>
-    <t>浙江巡抚署 浙江布政使司</t>
+    <t>浙江巡抚署|布政使司</t>
   </si>
   <si>
     <t>https://5b0988e595225.cdn.sohucs.com/images/20191127/bc38c7c521b14ba2baf63c932cd48742.jpeg</t>
@@ -255,7 +255,7 @@
     <t>何茂才</t>
   </si>
   <si>
-    <t>浙江按察使司 浙江布政使司</t>
+    <t>浙江按察使司|布政使司</t>
   </si>
   <si>
     <t>https://pic4.zhimg.com/v2-ba6876a60f9dc8147e5af8c603190159_r.jpg</t>
@@ -402,6 +402,9 @@
     <t>田有禄</t>
   </si>
   <si>
+    <t>淳安县衙</t>
+  </si>
+  <si>
     <t>https://pic.rmb.bdstatic.com/bjh/down/c73e2aa14974c1381b8101928dffef4b.jpeg</t>
   </si>
   <si>
@@ -447,7 +450,7 @@
     <t>鄢懋卿</t>
   </si>
   <si>
-    <t>刑部</t>
+    <t>刑部 盐务衙门</t>
   </si>
   <si>
     <t>000038</t>
@@ -1532,7 +1535,7 @@
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="14"/>
   <cols>
     <col min="1" max="2" width="15" customWidth="1"/>
-    <col min="3" max="3" width="25" customWidth="1"/>
+    <col min="3" max="3" width="44.0909090909091" customWidth="1"/>
     <col min="4" max="4" width="40" customWidth="1"/>
     <col min="5" max="10" width="15" customWidth="1"/>
   </cols>
@@ -2008,217 +2011,217 @@
         <v>121</v>
       </c>
       <c r="C33" t="s">
-        <v>107</v>
+        <v>122</v>
       </c>
       <c r="D33" t="s">
-        <v>122</v>
+        <v>123</v>
       </c>
     </row>
     <row r="34" spans="1:4">
       <c r="A34" s="5" t="s">
-        <v>123</v>
+        <v>124</v>
       </c>
       <c r="B34" t="s">
-        <v>124</v>
+        <v>125</v>
       </c>
       <c r="C34" t="s">
-        <v>125</v>
+        <v>126</v>
       </c>
       <c r="D34" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
     </row>
     <row r="35" spans="1:4">
       <c r="A35" s="5" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="B35" t="s">
-        <v>128</v>
+        <v>129</v>
       </c>
       <c r="C35" t="s">
-        <v>125</v>
+        <v>126</v>
       </c>
     </row>
     <row r="36" spans="1:4">
       <c r="A36" s="5" t="s">
-        <v>129</v>
+        <v>130</v>
       </c>
       <c r="B36" t="s">
-        <v>130</v>
+        <v>131</v>
       </c>
       <c r="C36" t="s">
         <v>87</v>
       </c>
       <c r="D36" s="4" t="s">
-        <v>131</v>
+        <v>132</v>
       </c>
     </row>
     <row r="37" spans="1:4">
       <c r="A37" s="5" t="s">
-        <v>132</v>
+        <v>133</v>
       </c>
       <c r="B37" t="s">
-        <v>133</v>
+        <v>134</v>
       </c>
       <c r="C37" t="s">
-        <v>134</v>
+        <v>135</v>
       </c>
     </row>
     <row r="38" spans="1:4">
       <c r="A38" s="5" t="s">
-        <v>135</v>
+        <v>136</v>
       </c>
       <c r="B38" t="s">
-        <v>136</v>
+        <v>137</v>
       </c>
       <c r="C38" t="s">
-        <v>137</v>
+        <v>138</v>
       </c>
     </row>
     <row r="39" spans="1:4">
       <c r="A39" s="5" t="s">
-        <v>138</v>
+        <v>139</v>
       </c>
       <c r="B39" t="s">
-        <v>139</v>
+        <v>140</v>
       </c>
       <c r="C39" t="s">
-        <v>140</v>
+        <v>141</v>
       </c>
       <c r="D39" t="s">
-        <v>141</v>
+        <v>142</v>
       </c>
     </row>
     <row r="40" spans="1:4">
       <c r="A40" s="5" t="s">
-        <v>142</v>
+        <v>143</v>
       </c>
       <c r="B40" t="s">
-        <v>143</v>
+        <v>144</v>
       </c>
       <c r="C40" t="s">
-        <v>144</v>
+        <v>145</v>
       </c>
       <c r="D40" s="4" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
     </row>
     <row r="41" spans="1:4">
       <c r="A41" s="5" t="s">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="B41" t="s">
-        <v>147</v>
+        <v>148</v>
       </c>
       <c r="C41" t="s">
         <v>77</v>
       </c>
       <c r="D41" t="s">
-        <v>148</v>
+        <v>149</v>
       </c>
     </row>
     <row r="42" spans="1:4">
       <c r="A42" s="5" t="s">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="B42" t="s">
-        <v>150</v>
+        <v>151</v>
       </c>
       <c r="C42" t="s">
         <v>77</v>
       </c>
       <c r="D42" t="s">
-        <v>151</v>
+        <v>152</v>
       </c>
     </row>
     <row r="43" spans="1:4">
       <c r="A43" s="5" t="s">
-        <v>152</v>
+        <v>153</v>
       </c>
       <c r="B43" t="s">
-        <v>153</v>
+        <v>154</v>
       </c>
       <c r="C43" t="s">
-        <v>154</v>
+        <v>155</v>
       </c>
       <c r="D43" t="s">
-        <v>155</v>
+        <v>156</v>
       </c>
     </row>
     <row r="44" spans="1:4">
       <c r="A44" s="5" t="s">
-        <v>156</v>
+        <v>157</v>
       </c>
       <c r="B44" t="s">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="C44" t="s">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="D44" t="s">
-        <v>159</v>
+        <v>160</v>
       </c>
     </row>
     <row r="45" spans="1:4">
       <c r="A45" s="5" t="s">
-        <v>160</v>
+        <v>161</v>
       </c>
       <c r="B45" t="s">
-        <v>161</v>
+        <v>162</v>
       </c>
       <c r="C45" t="s">
-        <v>162</v>
+        <v>163</v>
       </c>
       <c r="D45" t="s">
-        <v>163</v>
+        <v>164</v>
       </c>
     </row>
     <row r="46" spans="1:4">
       <c r="A46" s="5" t="s">
-        <v>164</v>
+        <v>165</v>
       </c>
       <c r="B46" t="s">
-        <v>165</v>
+        <v>166</v>
       </c>
       <c r="C46" t="s">
         <v>87</v>
       </c>
       <c r="D46" t="s">
-        <v>166</v>
+        <v>167</v>
       </c>
     </row>
     <row r="47" spans="1:4">
       <c r="A47" s="5" t="s">
-        <v>167</v>
+        <v>168</v>
       </c>
       <c r="B47" t="s">
-        <v>168</v>
+        <v>169</v>
       </c>
       <c r="C47" t="s">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="D47" t="s">
-        <v>170</v>
-      </c>
-    </row>
-    <row r="48" spans="1:4">
+        <v>171</v>
+      </c>
+    </row>
+    <row r="48" ht="13" customHeight="1" spans="1:4">
       <c r="A48" s="5" t="s">
-        <v>171</v>
+        <v>172</v>
       </c>
     </row>
     <row r="49" spans="1:1">
       <c r="A49" s="5" t="s">
-        <v>172</v>
+        <v>173</v>
       </c>
     </row>
     <row r="50" spans="1:1">
       <c r="A50" s="5" t="s">
-        <v>173</v>
+        <v>174</v>
       </c>
     </row>
     <row r="51" spans="1:1">
       <c r="A51" s="5" t="s">
-        <v>174</v>
+        <v>175</v>
       </c>
     </row>
   </sheetData>

--- a/public/excels/default-members.xlsx
+++ b/public/excels/default-members.xlsx
@@ -34,7 +34,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="189" uniqueCount="176">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="201" uniqueCount="188">
   <si>
     <t>employeeId</t>
   </si>
@@ -117,7 +117,7 @@
     <t>内阁 户部</t>
   </si>
   <si>
-    <t>https://pic.rmb.bdstatic.com/bjh/events/24cfb80c8e95f3fbca04251e633b4d211187.jpeg@h_1280</t>
+    <t>./images/xu-jie.png</t>
   </si>
   <si>
     <t>000006</t>
@@ -129,6 +129,9 @@
     <t>内阁 工部 吏部</t>
   </si>
   <si>
+    <t>./images/yan-shifan.png</t>
+  </si>
+  <si>
     <t>000007</t>
   </si>
   <si>
@@ -165,6 +168,9 @@
     <t>陈以勤</t>
   </si>
   <si>
+    <t>./images/chen-yiqin.png</t>
+  </si>
+  <si>
     <t>000011</t>
   </si>
   <si>
@@ -240,7 +246,7 @@
     <t>000017</t>
   </si>
   <si>
-    <t>郑必昌</t>
+    <t>郑泌昌</t>
   </si>
   <si>
     <t>浙江巡抚署|布政使司</t>
@@ -360,6 +366,9 @@
     <t>淳安县</t>
   </si>
   <si>
+    <t>./images/chang-boxi.png</t>
+  </si>
+  <si>
     <t>000028</t>
   </si>
   <si>
@@ -369,6 +378,9 @@
     <t>建德县</t>
   </si>
   <si>
+    <t>./images/zhang-zhiliang.png</t>
+  </si>
+  <si>
     <t>000029</t>
   </si>
   <si>
@@ -387,6 +399,9 @@
     <t>刘二</t>
   </si>
   <si>
+    <t>./images/liu-er.png</t>
+  </si>
+  <si>
     <t>000031</t>
   </si>
   <si>
@@ -396,6 +411,9 @@
     <t>台州卫 北镇抚司</t>
   </si>
   <si>
+    <t>./images/qi-dazhu.png</t>
+  </si>
+  <si>
     <t>000032</t>
   </si>
   <si>
@@ -426,6 +444,9 @@
     <t>徐千户</t>
   </si>
   <si>
+    <t>./images/xu-qianhu.png</t>
+  </si>
+  <si>
     <t>000035</t>
   </si>
   <si>
@@ -444,6 +465,9 @@
     <t>通政使司</t>
   </si>
   <si>
+    <t>./images/luo-longwen.png</t>
+  </si>
+  <si>
     <t>000037</t>
   </si>
   <si>
@@ -453,6 +477,9 @@
     <t>刑部 盐务衙门</t>
   </si>
   <si>
+    <t>./images/yan-maoqing.png</t>
+  </si>
+  <si>
     <t>000038</t>
   </si>
   <si>
@@ -553,6 +580,15 @@
   </si>
   <si>
     <t>000047</t>
+  </si>
+  <si>
+    <t>申时行</t>
+  </si>
+  <si>
+    <t>刑部</t>
+  </si>
+  <si>
+    <t>./images/shen-shixing.png</t>
   </si>
   <si>
     <t>000048</t>
@@ -1661,6 +1697,9 @@
       <c r="C7" t="s">
         <v>30</v>
       </c>
+      <c r="D7" t="s">
+        <v>31</v>
+      </c>
       <c r="E7">
         <v>50</v>
       </c>
@@ -1670,558 +1709,591 @@
     </row>
     <row r="8" spans="1:10">
       <c r="A8" s="5" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="B8" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="C8" t="s">
         <v>26</v>
       </c>
       <c r="D8" s="4" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
     </row>
     <row r="9" spans="1:10">
       <c r="A9" s="5" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="B9" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="C9" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="D9" s="4" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
     </row>
     <row r="10" spans="1:10">
       <c r="A10" s="5" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="B10" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="C10" t="s">
         <v>22</v>
       </c>
       <c r="D10" s="3" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
     </row>
     <row r="11" spans="1:10">
       <c r="A11" s="5" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="B11" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="C11" t="s">
         <v>22</v>
       </c>
+      <c r="D11" t="s">
+        <v>44</v>
+      </c>
     </row>
     <row r="12" spans="1:10">
       <c r="A12" s="5" t="s">
-        <v>43</v>
+        <v>45</v>
       </c>
       <c r="B12" t="s">
-        <v>44</v>
+        <v>46</v>
       </c>
       <c r="C12" t="s">
-        <v>45</v>
+        <v>47</v>
       </c>
       <c r="D12" t="s">
-        <v>46</v>
+        <v>48</v>
       </c>
     </row>
     <row r="13" spans="1:10">
       <c r="A13" s="5" t="s">
-        <v>47</v>
+        <v>49</v>
       </c>
       <c r="B13" t="s">
-        <v>48</v>
+        <v>50</v>
       </c>
       <c r="C13" t="s">
-        <v>49</v>
+        <v>51</v>
       </c>
       <c r="D13" s="4" t="s">
-        <v>50</v>
+        <v>52</v>
       </c>
     </row>
     <row r="14" spans="1:10">
       <c r="A14" s="5" t="s">
-        <v>51</v>
+        <v>53</v>
       </c>
       <c r="B14" t="s">
-        <v>52</v>
+        <v>54</v>
       </c>
       <c r="C14" t="s">
-        <v>53</v>
+        <v>55</v>
       </c>
       <c r="D14" t="s">
-        <v>54</v>
+        <v>56</v>
       </c>
     </row>
     <row r="15" spans="1:10">
       <c r="A15" s="5" t="s">
-        <v>55</v>
+        <v>57</v>
       </c>
       <c r="B15" t="s">
-        <v>56</v>
+        <v>58</v>
       </c>
       <c r="C15" t="s">
-        <v>57</v>
+        <v>59</v>
       </c>
       <c r="D15" t="s">
-        <v>58</v>
+        <v>60</v>
       </c>
     </row>
     <row r="16" spans="1:10">
       <c r="A16" s="5" t="s">
-        <v>59</v>
+        <v>61</v>
       </c>
       <c r="B16" t="s">
-        <v>60</v>
+        <v>62</v>
       </c>
       <c r="C16" t="s">
-        <v>61</v>
+        <v>63</v>
       </c>
       <c r="D16" s="3" t="s">
-        <v>62</v>
+        <v>64</v>
       </c>
     </row>
     <row r="17" spans="1:4">
       <c r="A17" s="5" t="s">
-        <v>63</v>
+        <v>65</v>
       </c>
       <c r="B17" t="s">
-        <v>64</v>
+        <v>66</v>
       </c>
       <c r="C17" t="s">
-        <v>65</v>
+        <v>67</v>
       </c>
       <c r="D17" t="s">
-        <v>66</v>
+        <v>68</v>
       </c>
     </row>
     <row r="18" spans="1:4">
       <c r="A18" s="5" t="s">
-        <v>67</v>
+        <v>69</v>
       </c>
       <c r="B18" t="s">
-        <v>68</v>
+        <v>70</v>
       </c>
       <c r="C18" t="s">
-        <v>69</v>
+        <v>71</v>
       </c>
       <c r="D18" t="s">
-        <v>70</v>
+        <v>72</v>
       </c>
     </row>
     <row r="19" spans="1:4">
       <c r="A19" s="5" t="s">
-        <v>71</v>
+        <v>73</v>
       </c>
       <c r="B19" t="s">
-        <v>72</v>
+        <v>74</v>
       </c>
       <c r="C19" t="s">
-        <v>73</v>
+        <v>75</v>
       </c>
       <c r="D19" t="s">
-        <v>74</v>
+        <v>76</v>
       </c>
     </row>
     <row r="20" spans="1:4">
       <c r="A20" s="5" t="s">
-        <v>75</v>
+        <v>77</v>
       </c>
       <c r="B20" t="s">
-        <v>76</v>
+        <v>78</v>
       </c>
       <c r="C20" t="s">
-        <v>77</v>
+        <v>79</v>
       </c>
       <c r="D20" t="s">
-        <v>78</v>
+        <v>80</v>
       </c>
     </row>
     <row r="21" spans="1:4">
       <c r="A21" s="5" t="s">
+        <v>81</v>
+      </c>
+      <c r="B21" t="s">
+        <v>82</v>
+      </c>
+      <c r="C21" t="s">
         <v>79</v>
       </c>
-      <c r="B21" t="s">
-        <v>80</v>
-      </c>
-      <c r="C21" t="s">
-        <v>77</v>
-      </c>
       <c r="D21" t="s">
-        <v>81</v>
+        <v>83</v>
       </c>
     </row>
     <row r="22" spans="1:4">
       <c r="A22" s="5" t="s">
-        <v>82</v>
+        <v>84</v>
       </c>
       <c r="B22" t="s">
-        <v>83</v>
+        <v>85</v>
       </c>
       <c r="C22" t="s">
-        <v>77</v>
+        <v>79</v>
       </c>
       <c r="D22" t="s">
-        <v>84</v>
+        <v>86</v>
       </c>
     </row>
     <row r="23" spans="1:4">
       <c r="A23" s="5" t="s">
-        <v>85</v>
+        <v>87</v>
       </c>
       <c r="B23" t="s">
-        <v>86</v>
+        <v>88</v>
       </c>
       <c r="C23" t="s">
-        <v>87</v>
+        <v>89</v>
       </c>
       <c r="D23" t="s">
-        <v>88</v>
+        <v>90</v>
       </c>
     </row>
     <row r="24" spans="1:4">
       <c r="A24" s="5" t="s">
-        <v>89</v>
+        <v>91</v>
       </c>
       <c r="B24" t="s">
-        <v>90</v>
+        <v>92</v>
       </c>
       <c r="C24" t="s">
-        <v>91</v>
+        <v>93</v>
       </c>
       <c r="D24" t="s">
-        <v>92</v>
+        <v>94</v>
       </c>
     </row>
     <row r="25" spans="1:4">
       <c r="A25" s="5" t="s">
-        <v>93</v>
+        <v>95</v>
       </c>
       <c r="B25" t="s">
-        <v>94</v>
+        <v>96</v>
       </c>
       <c r="C25" t="s">
-        <v>95</v>
+        <v>97</v>
       </c>
       <c r="D25" t="s">
-        <v>96</v>
+        <v>98</v>
       </c>
     </row>
     <row r="26" spans="1:4">
       <c r="A26" s="5" t="s">
-        <v>97</v>
+        <v>99</v>
       </c>
       <c r="B26" t="s">
-        <v>98</v>
+        <v>100</v>
       </c>
       <c r="C26" t="s">
-        <v>99</v>
+        <v>101</v>
       </c>
       <c r="D26" t="s">
-        <v>100</v>
+        <v>102</v>
       </c>
     </row>
     <row r="27" spans="1:4">
       <c r="A27" s="5" t="s">
-        <v>101</v>
+        <v>103</v>
       </c>
       <c r="B27" t="s">
-        <v>102</v>
+        <v>104</v>
       </c>
       <c r="C27" t="s">
-        <v>103</v>
+        <v>105</v>
       </c>
       <c r="D27" t="s">
-        <v>104</v>
+        <v>106</v>
       </c>
     </row>
     <row r="28" spans="1:4">
       <c r="A28" s="5" t="s">
-        <v>105</v>
+        <v>107</v>
       </c>
       <c r="B28" t="s">
-        <v>106</v>
+        <v>108</v>
       </c>
       <c r="C28" t="s">
-        <v>107</v>
+        <v>109</v>
+      </c>
+      <c r="D28" t="s">
+        <v>110</v>
       </c>
     </row>
     <row r="29" spans="1:4">
       <c r="A29" s="5" t="s">
-        <v>108</v>
+        <v>111</v>
       </c>
       <c r="B29" t="s">
-        <v>109</v>
+        <v>112</v>
       </c>
       <c r="C29" t="s">
-        <v>110</v>
+        <v>113</v>
+      </c>
+      <c r="D29" t="s">
+        <v>114</v>
       </c>
     </row>
     <row r="30" spans="1:4">
       <c r="A30" s="5" t="s">
-        <v>111</v>
+        <v>115</v>
       </c>
       <c r="B30" t="s">
-        <v>112</v>
+        <v>116</v>
       </c>
       <c r="C30" t="s">
-        <v>113</v>
+        <v>117</v>
       </c>
       <c r="D30" t="s">
-        <v>114</v>
+        <v>118</v>
       </c>
     </row>
     <row r="31" spans="1:4">
       <c r="A31" s="5" t="s">
-        <v>115</v>
+        <v>119</v>
       </c>
       <c r="B31" t="s">
-        <v>116</v>
+        <v>120</v>
       </c>
       <c r="C31" t="s">
-        <v>113</v>
+        <v>117</v>
+      </c>
+      <c r="D31" t="s">
+        <v>121</v>
       </c>
     </row>
     <row r="32" spans="1:4">
       <c r="A32" s="5" t="s">
-        <v>117</v>
+        <v>122</v>
       </c>
       <c r="B32" t="s">
-        <v>118</v>
+        <v>123</v>
       </c>
       <c r="C32" t="s">
-        <v>119</v>
+        <v>124</v>
+      </c>
+      <c r="D32" t="s">
+        <v>125</v>
       </c>
     </row>
     <row r="33" spans="1:4">
       <c r="A33" s="5" t="s">
-        <v>120</v>
+        <v>126</v>
       </c>
       <c r="B33" t="s">
-        <v>121</v>
+        <v>127</v>
       </c>
       <c r="C33" t="s">
-        <v>122</v>
+        <v>128</v>
       </c>
       <c r="D33" t="s">
-        <v>123</v>
+        <v>129</v>
       </c>
     </row>
     <row r="34" spans="1:4">
       <c r="A34" s="5" t="s">
-        <v>124</v>
+        <v>130</v>
       </c>
       <c r="B34" t="s">
-        <v>125</v>
+        <v>131</v>
       </c>
       <c r="C34" t="s">
-        <v>126</v>
+        <v>132</v>
       </c>
       <c r="D34" t="s">
-        <v>127</v>
+        <v>133</v>
       </c>
     </row>
     <row r="35" spans="1:4">
       <c r="A35" s="5" t="s">
-        <v>128</v>
+        <v>134</v>
       </c>
       <c r="B35" t="s">
-        <v>129</v>
+        <v>135</v>
       </c>
       <c r="C35" t="s">
-        <v>126</v>
+        <v>132</v>
+      </c>
+      <c r="D35" t="s">
+        <v>136</v>
       </c>
     </row>
     <row r="36" spans="1:4">
       <c r="A36" s="5" t="s">
-        <v>130</v>
+        <v>137</v>
       </c>
       <c r="B36" t="s">
-        <v>131</v>
+        <v>138</v>
       </c>
       <c r="C36" t="s">
-        <v>87</v>
+        <v>89</v>
       </c>
       <c r="D36" s="4" t="s">
-        <v>132</v>
+        <v>139</v>
       </c>
     </row>
     <row r="37" spans="1:4">
       <c r="A37" s="5" t="s">
-        <v>133</v>
+        <v>140</v>
       </c>
       <c r="B37" t="s">
-        <v>134</v>
+        <v>141</v>
       </c>
       <c r="C37" t="s">
-        <v>135</v>
+        <v>142</v>
+      </c>
+      <c r="D37" t="s">
+        <v>143</v>
       </c>
     </row>
     <row r="38" spans="1:4">
       <c r="A38" s="5" t="s">
-        <v>136</v>
+        <v>144</v>
       </c>
       <c r="B38" t="s">
-        <v>137</v>
+        <v>145</v>
       </c>
       <c r="C38" t="s">
-        <v>138</v>
+        <v>146</v>
+      </c>
+      <c r="D38" t="s">
+        <v>147</v>
       </c>
     </row>
     <row r="39" spans="1:4">
       <c r="A39" s="5" t="s">
-        <v>139</v>
+        <v>148</v>
       </c>
       <c r="B39" t="s">
-        <v>140</v>
+        <v>149</v>
       </c>
       <c r="C39" t="s">
-        <v>141</v>
+        <v>150</v>
       </c>
       <c r="D39" t="s">
-        <v>142</v>
+        <v>151</v>
       </c>
     </row>
     <row r="40" spans="1:4">
       <c r="A40" s="5" t="s">
-        <v>143</v>
+        <v>152</v>
       </c>
       <c r="B40" t="s">
-        <v>144</v>
+        <v>153</v>
       </c>
       <c r="C40" t="s">
-        <v>145</v>
+        <v>154</v>
       </c>
       <c r="D40" s="4" t="s">
-        <v>146</v>
+        <v>155</v>
       </c>
     </row>
     <row r="41" spans="1:4">
       <c r="A41" s="5" t="s">
-        <v>147</v>
+        <v>156</v>
       </c>
       <c r="B41" t="s">
-        <v>148</v>
+        <v>157</v>
       </c>
       <c r="C41" t="s">
-        <v>77</v>
+        <v>79</v>
       </c>
       <c r="D41" t="s">
-        <v>149</v>
+        <v>158</v>
       </c>
     </row>
     <row r="42" spans="1:4">
       <c r="A42" s="5" t="s">
-        <v>150</v>
+        <v>159</v>
       </c>
       <c r="B42" t="s">
-        <v>151</v>
+        <v>160</v>
       </c>
       <c r="C42" t="s">
-        <v>77</v>
+        <v>79</v>
       </c>
       <c r="D42" t="s">
-        <v>152</v>
+        <v>161</v>
       </c>
     </row>
     <row r="43" spans="1:4">
       <c r="A43" s="5" t="s">
-        <v>153</v>
+        <v>162</v>
       </c>
       <c r="B43" t="s">
-        <v>154</v>
+        <v>163</v>
       </c>
       <c r="C43" t="s">
-        <v>155</v>
+        <v>164</v>
       </c>
       <c r="D43" t="s">
-        <v>156</v>
+        <v>165</v>
       </c>
     </row>
     <row r="44" spans="1:4">
       <c r="A44" s="5" t="s">
-        <v>157</v>
+        <v>166</v>
       </c>
       <c r="B44" t="s">
-        <v>158</v>
+        <v>167</v>
       </c>
       <c r="C44" t="s">
-        <v>159</v>
+        <v>168</v>
       </c>
       <c r="D44" t="s">
-        <v>160</v>
+        <v>169</v>
       </c>
     </row>
     <row r="45" spans="1:4">
       <c r="A45" s="5" t="s">
-        <v>161</v>
+        <v>170</v>
       </c>
       <c r="B45" t="s">
-        <v>162</v>
+        <v>171</v>
       </c>
       <c r="C45" t="s">
-        <v>163</v>
+        <v>172</v>
       </c>
       <c r="D45" t="s">
-        <v>164</v>
+        <v>173</v>
       </c>
     </row>
     <row r="46" spans="1:4">
       <c r="A46" s="5" t="s">
-        <v>165</v>
+        <v>174</v>
       </c>
       <c r="B46" t="s">
-        <v>166</v>
+        <v>175</v>
       </c>
       <c r="C46" t="s">
-        <v>87</v>
+        <v>89</v>
       </c>
       <c r="D46" t="s">
-        <v>167</v>
+        <v>176</v>
       </c>
     </row>
     <row r="47" spans="1:4">
       <c r="A47" s="5" t="s">
-        <v>168</v>
+        <v>177</v>
       </c>
       <c r="B47" t="s">
-        <v>169</v>
+        <v>178</v>
       </c>
       <c r="C47" t="s">
-        <v>170</v>
+        <v>179</v>
       </c>
       <c r="D47" t="s">
-        <v>171</v>
+        <v>180</v>
       </c>
     </row>
     <row r="48" ht="13" customHeight="1" spans="1:4">
       <c r="A48" s="5" t="s">
-        <v>172</v>
+        <v>181</v>
+      </c>
+      <c r="B48" t="s">
+        <v>182</v>
+      </c>
+      <c r="C48" t="s">
+        <v>183</v>
+      </c>
+      <c r="D48" t="s">
+        <v>184</v>
       </c>
     </row>
     <row r="49" spans="1:1">
       <c r="A49" s="5" t="s">
-        <v>173</v>
+        <v>185</v>
       </c>
     </row>
     <row r="50" spans="1:1">
       <c r="A50" s="5" t="s">
-        <v>174</v>
+        <v>186</v>
       </c>
     </row>
     <row r="51" spans="1:1">
       <c r="A51" s="5" t="s">
-        <v>175</v>
+        <v>187</v>
       </c>
     </row>
   </sheetData>

--- a/public/excels/default-members.xlsx
+++ b/public/excels/default-members.xlsx
@@ -435,7 +435,7 @@
     <t>浙江按察使司</t>
   </si>
   <si>
-    <t>https://img2.baidu.com/it/u=3354097714,87429070&amp;fm=253&amp;fmt=auto&amp;app=138&amp;f=JPEG?w=607&amp;h=371</t>
+    <t>./images/jiang-qianhu.png</t>
   </si>
   <si>
     <t>000034</t>
